--- a/Exp3_PTO_GRPO/eda/results/arms/outcomes/tables/gpt-4o-mini/outcomes.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/outcomes/tables/gpt-4o-mini/outcomes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,15 +469,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>MIPROC %CR (MI process coder)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>Reflection:Question (MITI)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>% Complex Reflections (MITI)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>% MI-Consistent (MITI)</t>
         </is>
@@ -513,18 +518,21 @@
         <v>4.273</v>
       </c>
       <c r="I2" t="n">
-        <v>0.63</v>
+        <v>0.615</v>
       </c>
       <c r="J2" t="n">
         <v>0.491</v>
       </c>
       <c r="K2" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.75</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.364</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -558,18 +566,21 @@
         <v>4.258</v>
       </c>
       <c r="I3" t="n">
-        <v>0.638</v>
+        <v>0.676</v>
       </c>
       <c r="J3" t="n">
         <v>0.264</v>
       </c>
       <c r="K3" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.951</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.369</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>0.664</v>
       </c>
     </row>
@@ -603,18 +614,21 @@
         <v>3.922</v>
       </c>
       <c r="I4" t="n">
-        <v>0.574</v>
+        <v>0.583</v>
       </c>
       <c r="J4" t="n">
         <v>0.838</v>
       </c>
       <c r="K4" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="L4" t="n">
         <v>1.435</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.414</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>0.833</v>
       </c>
     </row>
@@ -648,18 +662,21 @@
         <v>4.536</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.732</v>
       </c>
       <c r="J5" t="n">
         <v>0.21</v>
       </c>
       <c r="K5" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="L5" t="n">
         <v>1.114</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.41</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>0.707</v>
       </c>
     </row>
@@ -693,18 +710,21 @@
         <v>4.273</v>
       </c>
       <c r="I6" t="n">
-        <v>0.63</v>
+        <v>0.615</v>
       </c>
       <c r="J6" t="n">
         <v>0.491</v>
       </c>
       <c r="K6" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.75</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.364</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -738,18 +758,21 @@
         <v>4.258</v>
       </c>
       <c r="I7" t="n">
-        <v>0.638</v>
+        <v>0.676</v>
       </c>
       <c r="J7" t="n">
         <v>0.264</v>
       </c>
       <c r="K7" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.951</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.369</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>0.664</v>
       </c>
     </row>
@@ -783,18 +806,21 @@
         <v>4.234</v>
       </c>
       <c r="I8" t="n">
-        <v>0.572</v>
+        <v>0.577</v>
       </c>
       <c r="J8" t="n">
         <v>0.535</v>
       </c>
       <c r="K8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="L8" t="n">
         <v>1.043</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>0.372</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>0.711</v>
       </c>
     </row>
@@ -828,18 +854,21 @@
         <v>4.536</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.732</v>
       </c>
       <c r="J9" t="n">
         <v>0.21</v>
       </c>
       <c r="K9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="L9" t="n">
         <v>1.114</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>0.41</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0.707</v>
       </c>
     </row>
